--- a/Snap1.xlsx
+++ b/Snap1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoj.TRANSITUSNEXGEN.000\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00BDD6C-E610-4337-86BC-81B9FECE76A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E40630-AFE3-4F32-8432-1B2FCB5E366C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
   <si>
     <t>TestScenarioID</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Rejected</t>
+  </si>
+  <si>
+    <t>Testing qwq</t>
   </si>
 </sst>
 </file>
@@ -881,7 +884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E17" t="s">
         <v>26</v>
       </c>
@@ -895,7 +898,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E18" t="s">
         <v>30</v>
       </c>
@@ -909,7 +912,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E19" t="s">
         <v>34</v>
       </c>
@@ -923,7 +926,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E20" t="s">
         <v>38</v>
       </c>
@@ -937,7 +940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
         <v>42</v>
       </c>
@@ -948,7 +951,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -973,8 +976,11 @@
       <c r="I22" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F23" t="s">
         <v>18</v>
       </c>
@@ -985,7 +991,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F24" t="s">
         <v>22</v>
       </c>
